--- a/Stats/StatCalc.xlsx
+++ b/Stats/StatCalc.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>Full Name</t>
   </si>
@@ -43,6 +43,9 @@
     <t>Abbr</t>
   </si>
   <si>
+    <t>Desc</t>
+  </si>
+  <si>
     <t>Multiplier</t>
   </si>
   <si>
@@ -64,28 +67,55 @@
     <t>con</t>
   </si>
   <si>
+    <t>max health, scales with level</t>
+  </si>
+  <si>
     <t>Strength</t>
   </si>
   <si>
     <t>str</t>
   </si>
   <si>
+    <t>phys damage</t>
+  </si>
+  <si>
     <t>Intelligence</t>
   </si>
   <si>
     <t>int</t>
   </si>
   <si>
+    <t>magic damage</t>
+  </si>
+  <si>
     <t>Technique</t>
   </si>
   <si>
     <t>tec</t>
   </si>
   <si>
+    <t>cast speed</t>
+  </si>
+  <si>
+    <t>1/4 cast time</t>
+  </si>
+  <si>
     <t>Agility</t>
   </si>
   <si>
-    <t>agi</t>
+    <t>agi-eva</t>
+  </si>
+  <si>
+    <t>slightly increases speed and evasion</t>
+  </si>
+  <si>
+    <t>25% evade</t>
+  </si>
+  <si>
+    <t>agi-spd</t>
+  </si>
+  <si>
+    <t>200% speed</t>
   </si>
 </sst>
 </file>
@@ -135,11 +165,8 @@
       <alignment horizontal="general" vertical="top"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0">
@@ -149,6 +176,12 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -466,245 +499,335 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{9CD09735-8A02-443F-A68F-EFA7E7956C84}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{28F15009-0AF7-49F7-9797-57BDECAAA184}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:T200"/>
   <sheetFormatPr defaultRowHeight="15" defaultColWidth="8.8515625" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="18.00390625" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" customWidth="1"/>
     <col min="5" max="5" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="1" customFormat="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2">
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1">
         <v>1</v>
       </c>
-      <c r="I1" s="2">
+      <c r="J1" s="1">
         <v>2</v>
       </c>
-      <c r="J1" s="2">
+      <c r="K1" s="1">
         <v>3</v>
       </c>
-      <c r="K1" s="2">
-        <v>4</v>
-      </c>
-      <c r="L1" s="2">
-        <v>5</v>
-      </c>
-      <c r="M1" s="2">
+      <c r="L1" s="1">
         <v>10</v>
       </c>
-      <c r="N1" s="2">
+      <c r="M1" s="1">
         <v>20</v>
       </c>
-      <c r="O1" s="2">
+      <c r="N1" s="1">
         <v>30</v>
       </c>
-      <c r="P1" s="2">
-        <v>40</v>
-      </c>
-      <c r="Q1" s="2">
+      <c r="O1" s="1">
         <v>50</v>
       </c>
-      <c r="R1" s="2"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="3">
-        <v>0.07</v>
-      </c>
-      <c r="D2" s="3">
+      <c r="B2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0.08</v>
+      </c>
+      <c r="E2" s="2">
         <v>100</v>
       </c>
-      <c r="E2" s="3">
+      <c r="F2" s="2">
         <v>0.03</v>
       </c>
-      <c r="F2" s="3">
+      <c r="G2" s="2">
         <v>100</v>
       </c>
-      <c r="G2" s="4">
-        <f t="shared" si="0" ref="G2:G3">(D2*(1+E2)^F2)</f>
-        <v>1921.86319808563</v>
-      </c>
-      <c r="H2" s="4">
-        <f>G2+G2*(1+(C2*H1))</f>
-        <v>3978.25682003725</v>
-      </c>
-      <c r="I2" s="4">
-        <f>G2+G2*(1+(C2*I1))</f>
-        <v>4112.78724390325</v>
-      </c>
-      <c r="J2" s="4">
-        <f>G2+G2*(1+(C2*J1))</f>
-        <v>4247.31766776924</v>
-      </c>
-      <c r="K2" s="4">
-        <f>G2+G2*(1+(C2*K1))</f>
-        <v>4381.84809163524</v>
-      </c>
-      <c r="L2" s="4">
-        <f>G2+G2*(1+(C2*L1))</f>
-        <v>4516.37851550123</v>
-      </c>
-      <c r="M2" s="4">
-        <f>G2+G2*(1+(C2*M1))</f>
-        <v>5189.0306348312</v>
-      </c>
-      <c r="N2" s="4">
-        <f>G2+G2*(1+(C2*N1))</f>
-        <v>6534.33487349114</v>
-      </c>
-      <c r="O2" s="4">
-        <f>G2+G2*(1+(C2*O1))</f>
-        <v>7879.63911215108</v>
-      </c>
-      <c r="P2" s="4">
-        <f>G2+G2*(1+(C2*P1))</f>
-        <v>9224.94335081103</v>
-      </c>
-      <c r="Q2" s="4">
-        <f>G2+G2*(1+(C2*Q1))</f>
-        <v>10570.247589471</v>
-      </c>
+      <c r="H2" s="2">
+        <f t="shared" si="0" ref="H2:H3">(E2*(1+(F2*G2)))</f>
+        <v>400</v>
+      </c>
+      <c r="I2" s="2">
+        <f>H2+(I1*(1+(D2*H2)))</f>
+        <v>433</v>
+      </c>
+      <c r="J2" s="2">
+        <f>H2+(J1*(1+(D2*H2)))</f>
+        <v>466</v>
+      </c>
+      <c r="K2" s="2">
+        <f>H2+(K1*(1+(D2*H2)))</f>
+        <v>499</v>
+      </c>
+      <c r="L2" s="2">
+        <f>H2+(L1*(1+(D2*H2)))</f>
+        <v>730</v>
+      </c>
+      <c r="M2" s="2">
+        <f>H2+(M1*(1+(D2*H2)))</f>
+        <v>1060</v>
+      </c>
+      <c r="N2" s="2">
+        <f>H2+(N1*(1+(D2*H2)))</f>
+        <v>1390</v>
+      </c>
+      <c r="O2" s="2">
+        <f>H2+(O1*(1+(D2*H2)))</f>
+        <v>2050</v>
+      </c>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="C3" s="3">
-        <v>0.07</v>
-      </c>
-      <c r="D3" s="3">
+      <c r="D3" s="2">
+        <v>0.08</v>
+      </c>
+      <c r="E3" s="2">
         <v>100</v>
       </c>
-      <c r="E3" s="3">
+      <c r="F3" s="2">
         <v>0.03</v>
       </c>
-      <c r="F3" s="3">
-        <v>10</v>
-      </c>
-      <c r="G3">
+      <c r="G3" s="2">
+        <v>25</v>
+      </c>
+      <c r="H3" s="2">
         <f t="shared" si="0"/>
-        <v>134.391637934412</v>
-      </c>
-      <c r="H3" s="4">
-        <f>G3+G3*(1+(C3*H1))</f>
-        <v>278.190690524233</v>
-      </c>
-      <c r="I3" s="4">
-        <f>G3+G3*(1+(C3*I1))</f>
-        <v>287.598105179642</v>
-      </c>
-      <c r="J3" s="4">
-        <f>G3+G3*(1+(C3*J1))</f>
-        <v>297.00551983505</v>
-      </c>
-      <c r="K3" s="4">
-        <f>G3+G3*(1+(C3*K1))</f>
-        <v>306.412934490459</v>
-      </c>
-      <c r="L3" s="4">
-        <f>G3+G3*(1+(C3*L1))</f>
-        <v>315.820349145868</v>
-      </c>
-      <c r="M3" s="4">
-        <f>G3+G3*(1+(C3*M1))</f>
-        <v>362.857422422912</v>
-      </c>
-      <c r="N3" s="4">
-        <f>G3+G3*(1+(C3*N1))</f>
-        <v>456.931568977001</v>
-      </c>
-      <c r="O3" s="4">
-        <f>G3+G3*(1+(C3*O1))</f>
-        <v>551.005715531089</v>
-      </c>
-      <c r="P3" s="4">
-        <f>G3+G3*(1+(C3*P1))</f>
-        <v>645.079862085178</v>
-      </c>
-      <c r="Q3" s="4">
-        <f>G3+G3*(1+(C3*Q1))</f>
-        <v>739.154008639266</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="I3" s="2">
+        <f>H3+(I1*(1+(D3*H3)))</f>
+        <v>190</v>
+      </c>
+      <c r="J3" s="2">
+        <f>H3+(J1*(1+(D3*H3)))</f>
+        <v>205</v>
+      </c>
+      <c r="K3" s="2">
+        <f>H3+(K1*(1+(D3*H3)))</f>
+        <v>220</v>
+      </c>
+      <c r="L3" s="2">
+        <f>H3+(L1*(1+(D3*H3)))</f>
+        <v>325</v>
+      </c>
+      <c r="M3" s="2">
+        <f>H3+(M1*(1+(D3*H3)))</f>
+        <v>475</v>
+      </c>
+      <c r="N3" s="2">
+        <f>H3+(N1*(1+(D3*H3)))</f>
+        <v>625</v>
+      </c>
+      <c r="O3" s="2">
+        <f>H3+(O1*(1+(D3*H3)))</f>
+        <v>925</v>
+      </c>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="3">
+      <c r="A4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="2">
         <v>0.05</v>
       </c>
-      <c r="D4" s="3">
+      <c r="E4" s="2">
         <v>100</v>
+      </c>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="2">
+        <f>E4+(I1*((D4*E4)))</f>
+        <v>105</v>
+      </c>
+      <c r="J4" s="2">
+        <f>E4+(J1*((D4*E4)))</f>
+        <v>110</v>
+      </c>
+      <c r="K4" s="3">
+        <v>115</v>
+      </c>
+      <c r="L4" s="3">
+        <v>200</v>
+      </c>
+      <c r="M4" s="3">
+        <v>400</v>
+      </c>
+      <c r="N4" s="3">
+        <v>600</v>
+      </c>
+      <c r="O4" s="3">
+        <v>1000</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="4">
+      <c r="A5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="2">
         <v>0.05</v>
       </c>
-      <c r="D5" s="4">
+      <c r="E5" s="2">
         <v>100</v>
       </c>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.05</v>
-      </c>
-      <c r="D6" s="4">
+      <c r="A6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0.015</v>
+      </c>
+      <c r="E6" s="2">
         <v>100</v>
+      </c>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="2">
+        <v>0.99</v>
+      </c>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="5">
+        <v>-0.2</v>
+      </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="4">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0.005</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="5">
+        <v>0.01</v>
+      </c>
+      <c r="K7" s="4"/>
+      <c r="L7" s="5">
         <v>0.05</v>
       </c>
-      <c r="D7" s="4">
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="B8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="E8" s="3">
         <v>100</v>
+      </c>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="5">
+        <v>0.02</v>
+      </c>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/Stats/StatCalc.xlsx
+++ b/Stats/StatCalc.xlsx
@@ -165,17 +165,11 @@
       <alignment horizontal="general" vertical="top"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -499,7 +493,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{28F15009-0AF7-49F7-9797-57BDECAAA184}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{8195507F-1359-438E-BA61-E1616E0A82E0}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:T200"/>
   <sheetFormatPr defaultRowHeight="15" defaultColWidth="8.8515625" customHeight="1"/>
   <cols>
@@ -565,7 +559,7 @@
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D2" s="2">
@@ -670,7 +664,7 @@
       <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D4" s="2">
@@ -679,9 +673,9 @@
       <c r="E4" s="2">
         <v>100</v>
       </c>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
       <c r="I4" s="2">
         <f>E4+(I1*((D4*E4)))</f>
         <v>105</v>
@@ -690,19 +684,19 @@
         <f>E4+(J1*((D4*E4)))</f>
         <v>110</v>
       </c>
-      <c r="K4" s="3">
+      <c r="K4" s="2">
         <v>115</v>
       </c>
-      <c r="L4" s="3">
+      <c r="L4" s="2">
         <v>200</v>
       </c>
-      <c r="M4" s="3">
+      <c r="M4" s="2">
         <v>400</v>
       </c>
-      <c r="N4" s="3">
+      <c r="N4" s="2">
         <v>600</v>
       </c>
-      <c r="O4" s="3">
+      <c r="O4" s="2">
         <v>1000</v>
       </c>
     </row>
@@ -713,7 +707,7 @@
       <c r="B5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D5" s="2">
@@ -722,16 +716,16 @@
       <c r="E5" s="2">
         <v>100</v>
       </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="2" t="s">
@@ -740,7 +734,7 @@
       <c r="B6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D6" s="2">
@@ -749,20 +743,20 @@
       <c r="E6" s="2">
         <v>100</v>
       </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
       <c r="I6" s="2">
         <v>0.99</v>
       </c>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="5">
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="3">
         <v>-0.2</v>
       </c>
-      <c r="N6" s="4"/>
-      <c r="O6" s="3" t="s">
+      <c r="N6" s="2"/>
+      <c r="O6" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -773,7 +767,7 @@
       <c r="B7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D7" s="2">
@@ -782,51 +776,51 @@
       <c r="E7" s="2">
         <v>0</v>
       </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="5">
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="3">
         <v>0.01</v>
       </c>
-      <c r="K7" s="4"/>
-      <c r="L7" s="5">
+      <c r="K7" s="2"/>
+      <c r="L7" s="3">
         <v>0.05</v>
       </c>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
-      <c r="O7" s="3" t="s">
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="2">
         <v>0.02</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="2">
         <v>100</v>
       </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="5">
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="3">
         <v>0.02</v>
       </c>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="5">
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="3">
         <v>0.2</v>
       </c>
-      <c r="M8" s="5">
+      <c r="M8" s="3">
         <v>0.4</v>
       </c>
-      <c r="N8" s="5">
+      <c r="N8" s="3">
         <v>0.6</v>
       </c>
-      <c r="O8" s="3" t="s">
+      <c r="O8" s="2" t="s">
         <v>26</v>
       </c>
     </row>

--- a/Stats/StatCalc.xlsx
+++ b/Stats/StatCalc.xlsx
@@ -493,7 +493,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{8195507F-1359-438E-BA61-E1616E0A82E0}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{D61BEC74-FEFC-4E29-B241-96CFD85260CA}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:T200"/>
   <sheetFormatPr defaultRowHeight="15" defaultColWidth="8.8515625" customHeight="1"/>
   <cols>

--- a/Stats/StatCalc.xlsx
+++ b/Stats/StatCalc.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>Full Name</t>
   </si>
@@ -61,6 +61,9 @@
     <t>New Base</t>
   </si>
   <si>
+    <t>notes</t>
+  </si>
+  <si>
     <t>Constitution</t>
   </si>
   <si>
@@ -79,6 +82,12 @@
     <t>phys damage</t>
   </si>
   <si>
+    <t>str-wgt</t>
+  </si>
+  <si>
+    <t>also helps with carryweight</t>
+  </si>
+  <si>
     <t>Intelligence</t>
   </si>
   <si>
@@ -116,13 +125,34 @@
   </si>
   <si>
     <t>200% speed</t>
+  </si>
+  <si>
+    <t>"Static" Stats</t>
+  </si>
+  <si>
+    <t>points represent overweight value</t>
+  </si>
+  <si>
+    <t>! overweight speed reduction capped at -90%</t>
+  </si>
+  <si>
+    <t>Weight</t>
+  </si>
+  <si>
+    <t>wgt</t>
+  </si>
+  <si>
+    <t>slows character down if overweight</t>
+  </si>
+  <si>
+    <t>this should scale higher than agility speed. So people should prioritize not being overweight</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <b val="0"/>
       <i val="0"/>
@@ -135,6 +165,14 @@
       <b/>
       <i val="0"/>
       <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i val="0"/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -165,7 +203,7 @@
       <alignment horizontal="general" vertical="top"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
@@ -173,6 +211,21 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -493,7 +546,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{D61BEC74-FEFC-4E29-B241-96CFD85260CA}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{69007769-BC6E-470E-A680-000713715B70}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:T200"/>
   <sheetFormatPr defaultRowHeight="15" defaultColWidth="8.8515625" customHeight="1"/>
   <cols>
@@ -550,17 +603,19 @@
       </c>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
+      <c r="R1" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" s="2">
         <v>0.08</v>
@@ -659,13 +714,13 @@
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="2">
         <v>0.05</v>
@@ -701,31 +756,36 @@
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="E5" s="2">
-        <v>100</v>
-      </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
+      <c r="D5" s="3">
+        <v>2</v>
+      </c>
+      <c r="I5" s="3">
+        <v>-22</v>
+      </c>
+      <c r="J5" s="3">
+        <v>-24</v>
+      </c>
+      <c r="K5" s="3">
+        <v>-26</v>
+      </c>
+      <c r="L5" s="3">
+        <v>-40</v>
+      </c>
+      <c r="M5" s="3">
+        <v>-60</v>
+      </c>
+      <c r="N5" s="3">
+        <v>-80</v>
+      </c>
+      <c r="O5" s="3">
+        <v>-120</v>
+      </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="2" t="s">
@@ -738,7 +798,7 @@
         <v>19</v>
       </c>
       <c r="D6" s="2">
-        <v>0.015</v>
+        <v>0.05</v>
       </c>
       <c r="E6" s="2">
         <v>100</v>
@@ -746,82 +806,185 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
-      <c r="I6" s="2">
-        <v>0.99</v>
-      </c>
+      <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
-      <c r="M6" s="3">
-        <v>-0.2</v>
-      </c>
+      <c r="M6" s="2"/>
       <c r="N6" s="2"/>
-      <c r="O6" s="2" t="s">
-        <v>20</v>
-      </c>
+      <c r="O6" s="2"/>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="D7" s="2">
-        <v>0.005</v>
+        <v>0.015</v>
       </c>
       <c r="E7" s="2">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="3">
-        <v>0.01</v>
-      </c>
+      <c r="I7" s="2">
+        <v>0.99</v>
+      </c>
+      <c r="J7" s="2"/>
       <c r="K7" s="2"/>
-      <c r="L7" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="M7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="4">
+        <v>-0.2</v>
+      </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
       <c r="B8" s="2" t="s">
         <v>25</v>
       </c>
+      <c r="C8" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="D8" s="2">
-        <v>0.02</v>
+        <v>0.005</v>
       </c>
       <c r="E8" s="2">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
-      <c r="I8" s="3">
+      <c r="I8" s="2"/>
+      <c r="J8" s="4">
+        <v>0.01</v>
+      </c>
+      <c r="K8" s="2"/>
+      <c r="L8" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="5"/>
+      <c r="B9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="5"/>
+      <c r="D9" s="2">
         <v>0.02</v>
       </c>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="3">
+      <c r="E9" s="2">
+        <v>100</v>
+      </c>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="4">
         <v>0.2</v>
       </c>
-      <c r="M8" s="3">
+      <c r="M9" s="4">
         <v>0.4</v>
       </c>
-      <c r="N8" s="3">
+      <c r="N9" s="4">
         <v>0.6</v>
       </c>
-      <c r="O8" s="2" t="s">
-        <v>26</v>
+      <c r="O9" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="3"/>
+    </row>
+    <row r="13" ht="22.41" customHeight="1" s="6" customFormat="1">
+      <c r="A13" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="6"/>
+      <c r="Q13" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="R13" s="6"/>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="3">
+        <v>-0.02</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="8">
+        <v>0.02</v>
+      </c>
+      <c r="J14" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="K14" s="8">
+        <v>0.06</v>
+      </c>
+      <c r="L14" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="M14" s="8">
+        <v>-0.4</v>
+      </c>
+      <c r="N14" s="8">
+        <v>-0.6</v>
+      </c>
+      <c r="O14" s="8">
+        <v>-0.9</v>
+      </c>
+      <c r="P14" s="5"/>
+      <c r="R14" s="3" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/Stats/StatCalc.xlsx
+++ b/Stats/StatCalc.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>Full Name</t>
   </si>
@@ -125,6 +125,21 @@
   </si>
   <si>
     <t>200% speed</t>
+  </si>
+  <si>
+    <t>slightly less cooldown</t>
+  </si>
+  <si>
+    <t>50% cooldown</t>
+  </si>
+  <si>
+    <t>Armor</t>
+  </si>
+  <si>
+    <t>amr</t>
+  </si>
+  <si>
+    <t>resist phys damage</t>
   </si>
   <si>
     <t>"Static" Stats</t>
@@ -203,14 +218,11 @@
       <alignment horizontal="general" vertical="top"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -222,13 +234,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -546,7 +555,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{69007769-BC6E-470E-A680-000713715B70}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{B2580B59-0D80-44FE-B6EE-A7FC43AFB0B8}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:T200"/>
   <sheetFormatPr defaultRowHeight="15" defaultColWidth="8.8515625" customHeight="1"/>
   <cols>
@@ -601,7 +610,9 @@
       <c r="O1" s="1">
         <v>50</v>
       </c>
-      <c r="P1" s="1"/>
+      <c r="P1" s="1">
+        <v>100</v>
+      </c>
       <c r="Q1" s="1"/>
       <c r="R1" s="1" t="s">
         <v>8</v>
@@ -756,34 +767,34 @@
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <v>2</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="2">
         <v>-22</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="2">
         <v>-24</v>
       </c>
-      <c r="K5" s="3">
+      <c r="K5" s="2">
         <v>-26</v>
       </c>
-      <c r="L5" s="3">
+      <c r="L5" s="2">
         <v>-40</v>
       </c>
-      <c r="M5" s="3">
+      <c r="M5" s="2">
         <v>-60</v>
       </c>
-      <c r="N5" s="3">
+      <c r="N5" s="2">
         <v>-80</v>
       </c>
-      <c r="O5" s="3">
+      <c r="O5" s="2">
         <v>-120</v>
       </c>
     </row>
@@ -839,7 +850,7 @@
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
-      <c r="M7" s="4">
+      <c r="M7" s="3">
         <v>-0.2</v>
       </c>
       <c r="N7" s="2"/>
@@ -867,11 +878,11 @@
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
-      <c r="J8" s="4">
+      <c r="J8" s="3">
         <v>0.01</v>
       </c>
       <c r="K8" s="2"/>
-      <c r="L8" s="4">
+      <c r="L8" s="3">
         <v>0.05</v>
       </c>
       <c r="M8" s="2"/>
@@ -881,11 +892,11 @@
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="5"/>
+      <c r="A9" s="2"/>
       <c r="B9" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="5"/>
+      <c r="C9" s="2"/>
       <c r="D9" s="2">
         <v>0.02</v>
       </c>
@@ -895,18 +906,18 @@
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
-      <c r="I9" s="4">
+      <c r="I9" s="3">
         <v>0.02</v>
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
-      <c r="L9" s="4">
+      <c r="L9" s="3">
         <v>0.2</v>
       </c>
-      <c r="M9" s="4">
+      <c r="M9" s="3">
         <v>0.4</v>
       </c>
-      <c r="N9" s="4">
+      <c r="N9" s="3">
         <v>0.6</v>
       </c>
       <c r="O9" s="2" t="s">
@@ -914,11 +925,97 @@
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="3"/>
-    </row>
-    <row r="13" ht="22.41" customHeight="1" s="6" customFormat="1">
-      <c r="A13" s="7" t="s">
+      <c r="A10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>30</v>
+      </c>
+      <c r="D10" s="4">
+        <v>-0.01</v>
+      </c>
+      <c r="E10" s="4">
+        <v>100</v>
+      </c>
+      <c r="I10">
+        <f>E10+(I1*((D10*E10)))</f>
+        <v>99</v>
+      </c>
+      <c r="J10" s="4">
+        <v>98</v>
+      </c>
+      <c r="K10" s="4">
+        <v>97</v>
+      </c>
+      <c r="L10" s="4">
+        <v>90</v>
+      </c>
+      <c r="M10" s="4">
+        <v>80</v>
+      </c>
+      <c r="N10" s="4">
+        <v>70</v>
+      </c>
+      <c r="O10" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="4">
+        <v>100</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5">
+        <f>(I1/(I1+D11))*100</f>
+        <v>0.99009900990099</v>
+      </c>
+      <c r="J11" s="5">
+        <f>(J1/(J1+D11))*100</f>
+        <v>1.96078431372549</v>
+      </c>
+      <c r="K11" s="5">
+        <f>(K1/(K1+D11))*100</f>
+        <v>2.9126213592233</v>
+      </c>
+      <c r="L11" s="5">
+        <f>(L1/(L1+D11))*100</f>
+        <v>9.09090909090909</v>
+      </c>
+      <c r="M11" s="5">
+        <f>(M1/(M1+D11))*100</f>
+        <v>16.6666666666667</v>
+      </c>
+      <c r="N11" s="5">
+        <f>(N1/(N1+D11))*100</f>
+        <v>23.0769230769231</v>
+      </c>
+      <c r="O11" s="5">
+        <f>(O1/(O1+D11))*100</f>
+        <v>33.3333333333333</v>
+      </c>
+      <c r="P11" s="5">
+        <f>(P1/(P1+D11))*100</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" ht="22.5" customHeight="1" s="6" customFormat="1">
+      <c r="A13" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -927,8 +1024,8 @@
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
-      <c r="I13" s="7" t="s">
-        <v>31</v>
+      <c r="I13" s="6" t="s">
+        <v>36</v>
       </c>
       <c r="J13" s="6"/>
       <c r="K13" s="6"/>
@@ -937,54 +1034,54 @@
       <c r="N13" s="6"/>
       <c r="O13" s="6"/>
       <c r="P13" s="6"/>
-      <c r="Q13" s="7" t="s">
-        <v>32</v>
+      <c r="Q13" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="R13" s="6"/>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" s="3">
+      <c r="A14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" s="2">
         <v>-0.02</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="2">
         <v>0</v>
       </c>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="8">
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="3">
         <v>0.02</v>
       </c>
-      <c r="J14" s="8">
+      <c r="J14" s="3">
         <v>0.04</v>
       </c>
-      <c r="K14" s="8">
+      <c r="K14" s="3">
         <v>0.06</v>
       </c>
-      <c r="L14" s="8">
+      <c r="L14" s="3">
         <v>0.2</v>
       </c>
-      <c r="M14" s="8">
+      <c r="M14" s="3">
         <v>-0.4</v>
       </c>
-      <c r="N14" s="8">
+      <c r="N14" s="3">
         <v>-0.6</v>
       </c>
-      <c r="O14" s="8">
+      <c r="O14" s="3">
         <v>-0.9</v>
       </c>
-      <c r="P14" s="5"/>
-      <c r="R14" s="3" t="s">
-        <v>36</v>
+      <c r="P14" s="2"/>
+      <c r="R14" s="2" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
